--- a/docs/tomtedetaljer-sandmoen.xlsx
+++ b/docs/tomtedetaljer-sandmoen.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Veiledning" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tomter'!$A$4:$P$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilder'!$A$4:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tomter'!$A$4:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bilder'!$A$4:$H$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -246,9 +246,9 @@
     <author>Sandmoen</author>
   </authors>
   <commentList>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="L4" authorId="0" shapeId="0">
       <text>
-        <t>Regnes ut automatisk fra kolonnene til venstre. «Komplett» betyr at utsikt, solforhold, beskrivelse og minst ett bilde er på plass.</t>
+        <t>Regnes ut automatisk fra kolonnene til venstre. «Komplett» betyr at beskrivelse og minst ett bilde er på plass.</t>
       </text>
     </comment>
   </commentList>
@@ -545,25 +545,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="46" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -605,65 +603,55 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Utsikt</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Solforhold</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
           <t>Beskrivelse av tomta
 (ingress øverst på tomtesiden)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Plassering i feltet
 (tekst over reguleringskartet)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Bilder
 (antall)</t>
         </is>
       </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Tekst under videoen</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Tekst under videoen</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Kart
 X %</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Kart
 Y %</t>
         </is>
       </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Mangler på nettsiden i dag</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>FRODE: tilføyelser og rettelser</t>
+        </is>
+      </c>
       <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>Mangler på nettsiden i dag</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>FRODE: tilføyelser og rettelser</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>FRODE:
 gjennomgått?</t>
@@ -689,42 +677,36 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Blåmuren</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
           <t>Tomta ligger på en kolle ca 140 meter fra parkeringsplass P3. Fra parkeringsplassen går det nå en bred opparbeidet sti til tomta. Strøm kan enkelt føres fram til hyttas plassering. Tomta ligger på en kolle og framstår lett bebyggelig.</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Tomta ligger mellom BFR 6 og BFR 8 og er merket aBF i reguleringskartet.</t>
-        </is>
-      </c>
-      <c r="I5" s="4">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Tomta ligger på en kolle ca 140 meter fra parkeringsplass P3. Fra parkeringsplassen går det en bred opparbeidet sti til tomta. Strøm kan enkelt føres fram til hyttas plassering. Tomta er ryddet, ligger på en kolle og framstår lett bebyggelig. Tomta ligger mellom BFR 6 og BFR 8 og er merket BF i reguleringskartet. (BFR = Byggeområde for fritidsbebyggelse.) Tomta utgjør 1 mål. Alle hytter i hyttefeltet har mulighet for å benytte seg av skutertransport etter nærmere avtale.</t>
+        </is>
+      </c>
+      <c r="G5" s="4">
         <f>COUNTIFS(Bilder!$A$5:$A$400,$A5,Bilder!$B$5:$B$400,"Bilde")</f>
         <v/>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="4" t="n">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="N5" s="5">
-        <f>IF(LEN(IF($E5="","Utsikt · ","")&amp;IF($F5="","Solforhold · ","")&amp;IF(OR($G5="",$G5="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I5=0,"Bilder · ",""))=0,"Komplett",LEFT(IF($E5="","Utsikt · ","")&amp;IF($F5="","Solforhold · ","")&amp;IF(OR($G5="",$G5="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I5=0,"Bilder · ",""),LEN(IF($E5="","Utsikt · ","")&amp;IF($F5="","Solforhold · ","")&amp;IF(OR($G5="",$G5="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I5=0,"Bilder · ",""))-3))</f>
+      <c r="L5" s="5">
+        <f>IF(LEN(IF(OR($E5="",$E5="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G5=0,"Bilder · ",""))=0,"Komplett",LEFT(IF(OR($E5="",$E5="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G5=0,"Bilder · ",""),LEN(IF(OR($E5="",$E5="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G5=0,"Bilder · ",""))-3))</f>
         <v/>
       </c>
-      <c r="O5" s="7" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
     </row>
     <row r="6" ht="118" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -743,36 +725,38 @@
       <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Mer informasjon kommer.</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="4">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Tomt 8 ligger ca 150 m fra parkeringsplass P4 og ca 210 meter fra parkeringsplass P3. På P4 er det ladestasjon for elbil. Tomta har god utsikt nordover, framstår lett bebyggelig og er frittliggende.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Tomt 8 ligger ca 150 m fra parkeringsplass P4 og ca 210 meter fra parkeringsplass P3. På P4 er det ladestasjon for elbil. Tomta har god utsikt nordover, framstår lett bebyggelig og er frittliggende. Fra byggegrensa til tomt 18 er det ca 40 meters avstand til byggegrensene til nabotomtene. Det er en eldre kjerrevei til en eldre rydningsrøyse som vil kunne benyttes som ferdselsvei til hytta. Tomta utgjør 1 mål. Alle hytter i hyttefeltet har mulighet for å benytte seg av skutertransport etter nærmere avtale.</t>
+        </is>
+      </c>
+      <c r="G6" s="4">
         <f>COUNTIFS(Bilder!$A$5:$A$400,$A6,Bilder!$B$5:$B$400,"Bilde")</f>
         <v/>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="4" t="n">
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="N6" s="5">
-        <f>IF(LEN(IF($E6="","Utsikt · ","")&amp;IF($F6="","Solforhold · ","")&amp;IF(OR($G6="",$G6="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I6=0,"Bilder · ",""))=0,"Komplett",LEFT(IF($E6="","Utsikt · ","")&amp;IF($F6="","Solforhold · ","")&amp;IF(OR($G6="",$G6="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I6=0,"Bilder · ",""),LEN(IF($E6="","Utsikt · ","")&amp;IF($F6="","Solforhold · ","")&amp;IF(OR($G6="",$G6="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I6=0,"Bilder · ",""))-3))</f>
+      <c r="L6" s="5">
+        <f>IF(LEN(IF(OR($E6="",$E6="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G6=0,"Bilder · ",""))=0,"Komplett",LEFT(IF(OR($E6="",$E6="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G6=0,"Bilder · ",""),LEN(IF(OR($E6="",$E6="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G6=0,"Bilder · ",""))-3))</f>
         <v/>
       </c>
-      <c r="O6" s="7" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="118" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -793,38 +777,36 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Nord og øst</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>Mer informasjon kommer.</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="4">
+          <t>Tomt 14 ligger på en kolle med flott utsikt mot Blåmuren og fjellområdene rundt. Tomta er ryddet og framstår lett bebyggelig.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Tomt 14 ligger på en kolle med flott utsikt mot Blåmuren og fjellområdene rundt. Tomta er ryddet og framstår lett bebyggelig. Fra byggegrensa til tomt 18 er det ca 50 meter til eksisterende hytte på BFR 15. Skogen skjermer BFR 14 fra eksisterende hytte. Avstanden fra byggegrensa på BFR 14 til byggegrensa på BFR 8 er ca 40 meter. Det er ca 90 meter fra BFR 14 til parkeringsplass P4. På P4 er det elbillader. Tilgangen til BFR 14 er lett framkommelig da en eksisterende opparbeidet og innregulert gangsti er etablert til BFR 15. Tomta utgjør 1 mål. Alle hytter i hyttefeltet har mulighet for å benytte seg av skutertransport etter nærmere avtale.</t>
+        </is>
+      </c>
+      <c r="G7" s="4">
         <f>COUNTIFS(Bilder!$A$5:$A$400,$A7,Bilder!$B$5:$B$400,"Bilde")</f>
         <v/>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
-      <c r="L7" s="4" t="n">
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="N7" s="5">
-        <f>IF(LEN(IF($E7="","Utsikt · ","")&amp;IF($F7="","Solforhold · ","")&amp;IF(OR($G7="",$G7="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I7=0,"Bilder · ",""))=0,"Komplett",LEFT(IF($E7="","Utsikt · ","")&amp;IF($F7="","Solforhold · ","")&amp;IF(OR($G7="",$G7="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I7=0,"Bilder · ",""),LEN(IF($E7="","Utsikt · ","")&amp;IF($F7="","Solforhold · ","")&amp;IF(OR($G7="",$G7="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I7=0,"Bilder · ",""))-3))</f>
+      <c r="L7" s="5">
+        <f>IF(LEN(IF(OR($E7="",$E7="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G7=0,"Bilder · ",""))=0,"Komplett",LEFT(IF(OR($E7="",$E7="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G7=0,"Bilder · ",""),LEN(IF(OR($E7="",$E7="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G7=0,"Bilder · ",""))-3))</f>
         <v/>
       </c>
-      <c r="O7" s="7" t="inlineStr"/>
-      <c r="P7" s="8" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="118" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -843,36 +825,38 @@
       <c r="D8" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Mer informasjon kommer.</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="4">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Tomt 17 er en frittliggende tomt på 1,2 mål med god utsikt mot nord. Noen større spredte grantrær skjermer hyttetomta, men kan også genere utsikten. Trærne vil bli hugget på forespørsel.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Tomt 17 er en frittliggende tomt på 1,2 mål med god utsikt mot nord. Noen større spredte grantrær skjermer hyttetomta, men kan også genere utsikten. Trærne vil bli hugget på forespørsel. Tomtas byggegrense ligger ca 55 meter fra byggegrensen til tomt 19. Det er planlagt å føre strøm til tomta fra tilkoblingsskapet mellom BFR 18 og BFR 20. Dette vil bli gjennomført etter nærmere avtale. Tomta ligger ca 300 meter fra parkeringsplass P4. Alle hytter i hyttefeltet har mulighet for å benytte seg av skutertransport etter nærmere avtale.</t>
+        </is>
+      </c>
+      <c r="G8" s="4">
         <f>COUNTIFS(Bilder!$A$5:$A$400,$A8,Bilder!$B$5:$B$400,"Bilde")</f>
         <v/>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr"/>
-      <c r="L8" s="4" t="n">
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="N8" s="5">
-        <f>IF(LEN(IF($E8="","Utsikt · ","")&amp;IF($F8="","Solforhold · ","")&amp;IF(OR($G8="",$G8="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I8=0,"Bilder · ",""))=0,"Komplett",LEFT(IF($E8="","Utsikt · ","")&amp;IF($F8="","Solforhold · ","")&amp;IF(OR($G8="",$G8="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I8=0,"Bilder · ",""),LEN(IF($E8="","Utsikt · ","")&amp;IF($F8="","Solforhold · ","")&amp;IF(OR($G8="",$G8="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I8=0,"Bilder · ",""))-3))</f>
+      <c r="L8" s="5">
+        <f>IF(LEN(IF(OR($E8="",$E8="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G8=0,"Bilder · ",""))=0,"Komplett",LEFT(IF(OR($E8="",$E8="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G8=0,"Bilder · ",""),LEN(IF(OR($E8="",$E8="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G8=0,"Bilder · ",""))-3))</f>
         <v/>
       </c>
-      <c r="O8" s="7" t="inlineStr"/>
-      <c r="P8" s="8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="118" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -893,38 +877,36 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Nord og øst</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
           <t>Panoramautsikt mot nord og øst, mot tomt 20. Strøm er framført.</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="4">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Tomt 18 er en tomt på 1,3 mål med svært god utsikt mot nord og øst. Tomta framstår lett bebyggelig og har strøm framført til tomtegrensa. Tomta er lett tilgjengelig ved å benytte eksisterende sti fra P4 til eksisterende hytte på BFR 20. Avstanden fra senter av tomta til eksisterende hytter på nabotomtene er ca 70 og 80 meter. Nivåforskjellen i terrenget skjermer hytta på BFR 16 fra tomt 18. Avstanden til parkeringsplass P4 er ca 260 meter. Alle hytter i hyttefeltet har mulighet for å benytte seg av skutertransport etter nærmere avtale.</t>
+        </is>
+      </c>
+      <c r="G9" s="4">
         <f>COUNTIFS(Bilder!$A$5:$A$400,$A9,Bilder!$B$5:$B$400,"Bilde")</f>
         <v/>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="4" t="n">
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="N9" s="5">
-        <f>IF(LEN(IF($E9="","Utsikt · ","")&amp;IF($F9="","Solforhold · ","")&amp;IF(OR($G9="",$G9="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I9=0,"Bilder · ",""))=0,"Komplett",LEFT(IF($E9="","Utsikt · ","")&amp;IF($F9="","Solforhold · ","")&amp;IF(OR($G9="",$G9="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I9=0,"Bilder · ",""),LEN(IF($E9="","Utsikt · ","")&amp;IF($F9="","Solforhold · ","")&amp;IF(OR($G9="",$G9="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($I9=0,"Bilder · ",""))-3))</f>
+      <c r="L9" s="5">
+        <f>IF(LEN(IF(OR($E9="",$E9="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G9=0,"Bilder · ",""))=0,"Komplett",LEFT(IF(OR($E9="",$E9="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G9=0,"Bilder · ",""),LEN(IF(OR($E9="",$E9="Mer informasjon kommer."),"Beskrivelse · ","")&amp;IF($G9=0,"Bilder · ",""))-3))</f>
         <v/>
       </c>
-      <c r="O9" s="7" t="inlineStr"/>
-      <c r="P9" s="8" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -952,62 +934,52 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Otersjøen og Blåmuren</t>
+          <t>Slak, tørr furumo med fjell i dagen mot vest. Bilvei fram til P3, derfra ca 80 meter på opparbeidet sti.</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>Kveldssol</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
-        <is>
-          <t>Slak, tørr furumo med fjell i dagen mot vest. Bilvei fram til P3, derfra ca 80 meter på opparbeidet sti.</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
           <t>Ligger mellom BFR 17 og BFR 18, merket bBF i reguleringskartet.</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="G12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Nei</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr"/>
-      <c r="L12" s="10" t="n">
+      <c r="I12" s="11" t="inlineStr"/>
+      <c r="J12" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="K12" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="N12" s="11" t="inlineStr"/>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Tar nye bilder til høsten.</t>
         </is>
       </c>
-      <c r="P12" s="10" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P9"/>
+  <autoFilter ref="A4:N9"/>
   <mergeCells count="2">
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C5:C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Ledig,Reservert,Festet"</formula1>
     </dataValidation>
-    <dataValidation sqref="P5:P9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Ja,Nei"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1024,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2306,60 +2278,210 @@
       <c r="H46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="n">
+      <c r="A47" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr"/>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>tomt18-sommer26.mp4</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Knappen «Se video fra tomta»</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Bilde</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>tomt18-vinter-1.jpeg</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Kun i bildevisningen («+ N bilder»)</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
       <c r="G47" s="8" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="n">
+      <c r="A48" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>Video-plakat</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr"/>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>tomt18-sommer26-poster.jpeg</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>Stillbildet før videoen starter</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr"/>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Bilde</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>tomt18-vinter-2.jpeg</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Kun i bildevisningen («+ N bilder»)</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
       <c r="G48" s="8" t="inlineStr"/>
       <c r="H48" s="7" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Bilde</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>tomt18-vinter-3.jpeg</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Kun i bildevisningen («+ N bilder»)</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Bilde</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>tomt18-panorama-1.jpeg</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Kun i bildevisningen («+ N bilder»)</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G50" s="8" t="inlineStr"/>
+      <c r="H50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Bilde</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>tomt18-panorama-2.jpeg</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Kun i bildevisningen («+ N bilder»)</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>standard</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr"/>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>tomt18-sommer26.mp4</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>Knappen «Se video fra tomta»</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr"/>
+      <c r="G52" s="8" t="inlineStr"/>
+      <c r="H52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>Video-plakat</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr"/>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>tomt18-sommer26-poster.jpeg</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>Stillbildet før videoen starter</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H48"/>
+  <autoFilter ref="A4:H53"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5:G48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5:G53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Ja,Nei,Byttes"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2375,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2455,17 +2577,15 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Merknad om vann, vei og strøm</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Strøm er framført til feltet. Vann og vei er ikke opparbeidet.</t>
-        </is>
+          <t>Kommunale kostnader</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>21500</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Oversikt, hver tomteside, kontakt</t>
+          <t>Oversikten («Hyttetomter til feste»)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
@@ -2473,17 +2593,17 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>«Dette følger med» – punkt 1</t>
+          <t>Merknad om vann, vei og strøm</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Enkel strømtilknytning</t>
+          <t>Strøm er framført til feltet. Vann og vei er ikke opparbeidet.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Hver tomteside</t>
+          <t>Oversikt, hver tomteside, kontakt</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -2491,12 +2611,12 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>«Dette følger med» – punkt 2</t>
+          <t>«Dette følger med» – punkt 1</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Gode jakt- og fiskemuligheter</t>
+          <t>Enkel strømtilknytning</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2509,12 +2629,12 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>«Dette følger med» – punkt 3</t>
+          <t>«Dette følger med» – punkt 2</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Godt ski- og jaktterreng</t>
+          <t>Gode jakt- og fiskemuligheter</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2527,12 +2647,12 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>«Dette følger med» – punkt 4</t>
+          <t>«Dette følger med» – punkt 3</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Kort vei til Lierne kommune sitt løypenett for snøscooter</t>
+          <t>Godt ski- og jaktterreng</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2545,12 +2665,12 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>«Dette følger med» – punkt 5</t>
+          <t>«Dette følger med» – punkt 4</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Nær Blåfjella-Skjækerfjella og Lierne nasjonalparker</t>
+          <t>Kort vei til Lierne kommune sitt løypenett for snøscooter</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2563,17 +2683,17 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Tekst under hero-videoen</t>
+          <t>«Dette følger med» – punkt 5</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Tomt 14 · F4 grense nord · Høst</t>
+          <t>Nær Blåfjella-Skjækerfjella og Lierne nasjonalparker</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Forsiden</t>
+          <t>Hver tomteside</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -2581,17 +2701,17 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Stedsnavn</t>
+          <t>Tekst under hero-videoen</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Sandmoen</t>
+          <t>Tomt 14 · F4 grense nord · Høst</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Topplinje og bunntekst på alle sider</t>
+          <t>Forsiden</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -2599,17 +2719,17 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Undertittel</t>
+          <t>Stedsnavn</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Hyttetomter ved Otersjøen · Lierne</t>
+          <t>Sandmoen</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Topplinje og bunntekst</t>
+          <t>Topplinje og bunntekst på alle sider</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
@@ -2617,17 +2737,17 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Feltnavn</t>
+          <t>Undertittel</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Felt 4 · Lifjellet i Lierne</t>
+          <t>Hyttetomter ved Otersjøen · Lierne</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Forsiden og hver tomteside</t>
+          <t>Topplinje og bunntekst</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -2635,17 +2755,17 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Kontaktperson</t>
+          <t>Feltnavn</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Frode Skjelbred</t>
+          <t>Felt 4 · Lifjellet i Lierne</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Bunntekst og kontaktsiden</t>
+          <t>Forsiden og hver tomteside</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
@@ -2653,12 +2773,12 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Telefon</t>
+          <t>Kontaktperson</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>472 774 42</t>
+          <t>Frode Skjelbred</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2671,12 +2791,12 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>E-post</t>
+          <t>Telefon</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>post@sandmoen.com</t>
+          <t>472 774 42</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2689,20 +2809,74 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>E-post</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>post@sandmoen.com</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Bunntekst og kontaktsiden</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>Lenke til reguleringsplanen</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>https://kommunekart.com/klient/IndreNamdal?urlid=98245ea4-4583-4aa0-9a64-fff3153b4252</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Hver tomteside</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Oversikten og hver tomteside</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Lenke til tomtefesteloven</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>https://lovdata.no/dokument/NL/lov/1996-12-20-106</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>«Slik fester du tomt» på oversikten</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Lenke om nasjonalparken</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.norgesnasjonalparker.no/nasjonalparker/blafjella-skjakerfjella/</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Oversikten og hver tomteside</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2717,7 +2891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2903,172 +3077,138 @@
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Utsikt</t>
+          <t>Beskrivelse av tomta</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Kort stikkord, f.eks. «Blåmuren» eller «Nord og øst». Brukes også som filtervalg i oversikten.</t>
+          <t>Ingressen øverst på tomtesiden, og teksten på kortet i oversikten. To–fire setninger om terreng, adkomst, strøm og hva som gjør tomta spesiell.</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Faktaboks og filter</t>
+          <t>Tomtesiden og oversiktskortet</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Solforhold</t>
+          <t>Plassering i feltet</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Kort stikkord, f.eks. «Kveldssol» eller «Sol hele dagen». Står tomt på alle tomtene i dag og vises som «Kommer».</t>
+          <t>Setningen over reguleringskartet, som forklarer hvor tomta ligger i forhold til naboene. Står den tom, skrives «I reguleringsplanen er dette BFR N» automatisk.</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Faktaboks</t>
+          <t>Tomtesiden</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Beskrivelse av tomta</t>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Ingressen øverst på tomtesiden, og teksten på kortet i oversikten. To–fire setninger om terreng, adkomst, strøm og hva som gjør tomta spesiell.</t>
+          <t>Antall bilder på tomta. Detaljene ligger på arket «Bilder».</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Tomtesiden og oversiktskortet</t>
+          <t>Galleri på tomtesiden</t>
         </is>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Plassering i feltet</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Setningen over reguleringskartet, som forklarer hvor tomta ligger i forhold til naboene. Står den tom, skrives «I reguleringsplanen er dette BFR N» automatisk.</t>
+          <t>Om tomta har video. Alle fem har sommervideo fra 2026.</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Tomtesiden</t>
+          <t>Knappen «Se video fra tomta»</t>
         </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Bilder</t>
+          <t>Tekst under videoen</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Antall bilder på tomta. Detaljene ligger på arket «Bilder».</t>
+          <t>Valgfri bildetekst i videovinduet, f.eks. «Tomt 14 · F4 grense nord · Høst».</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Galleri på tomtesiden</t>
+          <t>Videovinduet</t>
         </is>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Kart X og Y</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Om tomta har video. Alle fem har sommervideo fra 2026.</t>
+          <t>Hvor tomtenålen står i kartvisningen i oversikten, målt i prosent av bredde og høyde. Bare relevant hvis nålen står feil.</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Knappen «Se video fra tomta»</t>
+          <t>Kartvisningen i oversikten</t>
         </is>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Tekst under videoen</t>
+          <t>Mangler på nettsiden i dag</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Valgfri bildetekst i videovinduet, f.eks. «Tomt 14 · F4 grense nord · Høst».</t>
+          <t>Regnes ut automatisk. «Komplett» betyr at beskrivelse og bilder er på plass.</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Videovinduet</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Kart X og Y</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Hvor tomtenålen står i kartvisningen i oversikten, målt i prosent av bredde og høyde. Bare relevant hvis nålen står feil.</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Kartvisningen i oversikten</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Mangler på nettsiden i dag</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Regnes ut automatisk. «Komplett» betyr at utsikt, solforhold, beskrivelse og bilder er på plass.</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
           <t>Vises ikke på nettsiden</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Ikke med i arket</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>Feltet har 15 tomter totalt. Bare de fem som er til feste nå (7, 8, 14, 17 og 18) ligger på nettsiden og i dette arket. Skal flere legges ut, sier du fra, så føyer vi dem til.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Bilder legges ikke inn i arket – de bearbeides fra originalfilene. Skriv i kommentarfeltet hvilke som skal byttes, så tar vi det derfra.</t>
         </is>
@@ -3076,12 +3216,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
